--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -879,6 +879,31 @@
         <v>22936.76</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5.1259</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5.9573</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.9373</v>
+      </c>
+      <c r="E19" t="n">
+        <v>406703.05</v>
+      </c>
+      <c r="F19" t="n">
+        <v>185147.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>22946.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -904,6 +904,31 @@
         <v>22946.6</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5.1162</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5.9389</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.9276</v>
+      </c>
+      <c r="E20" t="n">
+        <v>400499.67</v>
+      </c>
+      <c r="F20" t="n">
+        <v>185147.16</v>
+      </c>
+      <c r="G20" t="n">
+        <v>22667.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -929,6 +929,31 @@
         <v>22667.84</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5.0878</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.9238</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6.8946</v>
+      </c>
+      <c r="E21" t="n">
+        <v>404403.73</v>
+      </c>
+      <c r="F21" t="n">
+        <v>187366.84</v>
+      </c>
+      <c r="G21" t="n">
+        <v>22594.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -954,6 +954,31 @@
         <v>22594.41</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5.1303</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.9612</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6.9345</v>
+      </c>
+      <c r="E22" t="n">
+        <v>398261.03</v>
+      </c>
+      <c r="F22" t="n">
+        <v>185629.05</v>
+      </c>
+      <c r="G22" t="n">
+        <v>22644.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -979,6 +979,31 @@
         <v>22644.63</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5.1068</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5.922</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6.9025</v>
+      </c>
+      <c r="E23" t="n">
+        <v>393162.88</v>
+      </c>
+      <c r="F23" t="n">
+        <v>188268.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22336.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1004,6 +1004,31 @@
         <v>22336.12</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5.1262</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5.9423</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6.9309</v>
+      </c>
+      <c r="E24" t="n">
+        <v>396388.28</v>
+      </c>
+      <c r="F24" t="n">
+        <v>187206.89</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22600.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1029,6 +1029,31 @@
         <v>22600.9</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5.1262</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5.9463</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6.9356</v>
+      </c>
+      <c r="E25" t="n">
+        <v>393174.67</v>
+      </c>
+      <c r="F25" t="n">
+        <v>187206.89</v>
+      </c>
+      <c r="G25" t="n">
+        <v>22600.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1054,6 +1054,31 @@
         <v>22600.9</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5.1649</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5.961</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6.9639</v>
+      </c>
+      <c r="E26" t="n">
+        <v>405774.02</v>
+      </c>
+      <c r="F26" t="n">
+        <v>184427.48</v>
+      </c>
+      <c r="G26" t="n">
+        <v>22236.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1079,6 +1079,31 @@
         <v>22236.96</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5.1305</v>
+      </c>
+      <c r="C27" t="n">
+        <v>5.927</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6.9207</v>
+      </c>
+      <c r="E27" t="n">
+        <v>394778.33</v>
+      </c>
+      <c r="F27" t="n">
+        <v>185500.88</v>
+      </c>
+      <c r="G27" t="n">
+        <v>22214.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1104,6 +1104,31 @@
         <v>22214.55</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5.1492</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5.9375</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6.9274</v>
+      </c>
+      <c r="E28" t="n">
+        <v>390849.92</v>
+      </c>
+      <c r="F28" t="n">
+        <v>186502.64</v>
+      </c>
+      <c r="G28" t="n">
+        <v>22574.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1129,6 +1129,31 @@
         <v>22574.09</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5.1331</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5.8964</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6.8691</v>
+      </c>
+      <c r="E29" t="n">
+        <v>393867.18</v>
+      </c>
+      <c r="F29" t="n">
+        <v>185547.66</v>
+      </c>
+      <c r="G29" t="n">
+        <v>22604.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1154,6 +1154,31 @@
         <v>22604.63</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5.1383</v>
+      </c>
+      <c r="C30" t="n">
+        <v>5.8869</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6.8523</v>
+      </c>
+      <c r="E30" t="n">
+        <v>400539.48</v>
+      </c>
+      <c r="F30" t="n">
+        <v>185992.03</v>
+      </c>
+      <c r="G30" t="n">
+        <v>22637.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1179,31 @@
         <v>22637.29</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5.1421</v>
+      </c>
+      <c r="C31" t="n">
+        <v>5.9057</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6.8886</v>
+      </c>
+      <c r="E31" t="n">
+        <v>418170.84</v>
+      </c>
+      <c r="F31" t="n">
+        <v>185229.17</v>
+      </c>
+      <c r="G31" t="n">
+        <v>22753.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1204,6 +1204,31 @@
         <v>22753.28</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5.1421</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5.9057</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6.8886</v>
+      </c>
+      <c r="E32" t="n">
+        <v>413027.15</v>
+      </c>
+      <c r="F32" t="n">
+        <v>185229.17</v>
+      </c>
+      <c r="G32" t="n">
+        <v>22753.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1229,6 +1229,31 @@
         <v>22753.28</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5.108</v>
+      </c>
+      <c r="C33" t="n">
+        <v>5.8628</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6.8351</v>
+      </c>
+      <c r="E33" t="n">
+        <v>438291.99</v>
+      </c>
+      <c r="F33" t="n">
+        <v>185653.22</v>
+      </c>
+      <c r="G33" t="n">
+        <v>22361.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1254,6 +1254,31 @@
         <v>22361.8</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>5.1317</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5.8803</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6.8561</v>
+      </c>
+      <c r="E34" t="n">
+        <v>441302.03</v>
+      </c>
+      <c r="F34" t="n">
+        <v>186595.6</v>
+      </c>
+      <c r="G34" t="n">
+        <v>22433.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1279,6 +1279,31 @@
         <v>22433.23</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>5.1334</v>
+      </c>
+      <c r="C35" t="n">
+        <v>5.8574</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6.8169</v>
+      </c>
+      <c r="E35" t="n">
+        <v>437786.67</v>
+      </c>
+      <c r="F35" t="n">
+        <v>187422.92</v>
+      </c>
+      <c r="G35" t="n">
+        <v>22293.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1304,6 +1304,31 @@
         <v>22293.84</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5.165</v>
+      </c>
+      <c r="C36" t="n">
+        <v>5.8788</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6.8393</v>
+      </c>
+      <c r="E36" t="n">
+        <v>431809.7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>185814.1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>22260.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1329,6 +1329,31 @@
         <v>22260.12</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>5.1948</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5.9253</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6.8897</v>
+      </c>
+      <c r="E37" t="n">
+        <v>438659.35</v>
+      </c>
+      <c r="F37" t="n">
+        <v>183965.9</v>
+      </c>
+      <c r="G37" t="n">
+        <v>22516.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1354,6 +1354,31 @@
         <v>22516.34</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5.1866</v>
+      </c>
+      <c r="C38" t="n">
+        <v>5.9081</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6.8688</v>
+      </c>
+      <c r="E38" t="n">
+        <v>436246.9</v>
+      </c>
+      <c r="F38" t="n">
+        <v>183476.86</v>
+      </c>
+      <c r="G38" t="n">
+        <v>22412.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1379,6 +1379,31 @@
         <v>22412.34</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5.1866</v>
+      </c>
+      <c r="C39" t="n">
+        <v>5.9081</v>
+      </c>
+      <c r="D39" t="n">
+        <v>6.8688</v>
+      </c>
+      <c r="E39" t="n">
+        <v>440023.31</v>
+      </c>
+      <c r="F39" t="n">
+        <v>183476.86</v>
+      </c>
+      <c r="G39" t="n">
+        <v>22412.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1404,6 +1404,31 @@
         <v>22412.34</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>5.2151</v>
+      </c>
+      <c r="C40" t="n">
+        <v>5.9306</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6.9164</v>
+      </c>
+      <c r="E40" t="n">
+        <v>435392.01</v>
+      </c>
+      <c r="F40" t="n">
+        <v>183160.81</v>
+      </c>
+      <c r="G40" t="n">
+        <v>21670.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1429,6 +1429,31 @@
         <v>21670.83</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5.2104</v>
+      </c>
+      <c r="C41" t="n">
+        <v>5.9122</v>
+      </c>
+      <c r="D41" t="n">
+        <v>6.8937</v>
+      </c>
+      <c r="E41" t="n">
+        <v>437887.54</v>
+      </c>
+      <c r="F41" t="n">
+        <v>182684.88</v>
+      </c>
+      <c r="G41" t="n">
+        <v>21885.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1454,6 +1454,31 @@
         <v>21885.24</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5.1726</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5.879</v>
+      </c>
+      <c r="D42" t="n">
+        <v>6.8738</v>
+      </c>
+      <c r="E42" t="n">
+        <v>434233.1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>185786.98</v>
+      </c>
+      <c r="G42" t="n">
+        <v>21790.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1479,6 +1479,31 @@
         <v>21790.09</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>5.219</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5.8746</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6.8931</v>
+      </c>
+      <c r="E43" t="n">
+        <v>437961.47</v>
+      </c>
+      <c r="F43" t="n">
+        <v>186053.47</v>
+      </c>
+      <c r="G43" t="n">
+        <v>21890.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1504,6 +1504,31 @@
         <v>21890.05</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>5.2215</v>
+      </c>
+      <c r="C44" t="n">
+        <v>5.8901</v>
+      </c>
+      <c r="D44" t="n">
+        <v>6.9136</v>
+      </c>
+      <c r="E44" t="n">
+        <v>451665.49</v>
+      </c>
+      <c r="F44" t="n">
+        <v>187329.12</v>
+      </c>
+      <c r="G44" t="n">
+        <v>22008.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1529,6 +1529,31 @@
         <v>22008.62</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>5.2223</v>
+      </c>
+      <c r="C45" t="n">
+        <v>5.8702</v>
+      </c>
+      <c r="D45" t="n">
+        <v>6.9084</v>
+      </c>
+      <c r="E45" t="n">
+        <v>443014.55</v>
+      </c>
+      <c r="F45" t="n">
+        <v>192114.55</v>
+      </c>
+      <c r="G45" t="n">
+        <v>21736.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1554,6 +1554,31 @@
         <v>21736.78</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5.2223</v>
+      </c>
+      <c r="C46" t="n">
+        <v>5.8702</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6.9084</v>
+      </c>
+      <c r="E46" t="n">
+        <v>445184.42</v>
+      </c>
+      <c r="F46" t="n">
+        <v>192114.55</v>
+      </c>
+      <c r="G46" t="n">
+        <v>21736.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1579,6 +1579,31 @@
         <v>21736.78</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>04/10/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4.9855</v>
+      </c>
+      <c r="C47" t="n">
+        <v>5.5886</v>
+      </c>
+      <c r="D47" t="n">
+        <v>6.591</v>
+      </c>
+      <c r="E47" t="n">
+        <v>424894.62</v>
+      </c>
+      <c r="F47" t="n">
+        <v>209251.08</v>
+      </c>
+      <c r="G47" t="n">
+        <v>20711.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1604,6 +1604,31 @@
         <v>20711.76</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4.9638</v>
+      </c>
+      <c r="C48" t="n">
+        <v>5.5931</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.5975</v>
+      </c>
+      <c r="E48" t="n">
+        <v>427639.06</v>
+      </c>
+      <c r="F48" t="n">
+        <v>205229.11</v>
+      </c>
+      <c r="G48" t="n">
+        <v>20717.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1629,6 +1629,31 @@
         <v>20717.91</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4.991</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.5867</v>
+      </c>
+      <c r="D49" t="n">
+        <v>6.5968</v>
+      </c>
+      <c r="E49" t="n">
+        <v>414017.23</v>
+      </c>
+      <c r="F49" t="n">
+        <v>204862.81</v>
+      </c>
+      <c r="G49" t="n">
+        <v>20614.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1654,6 +1654,31 @@
         <v>20614.83</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5.0071</v>
+      </c>
+      <c r="C50" t="n">
+        <v>5.6172</v>
+      </c>
+      <c r="D50" t="n">
+        <v>6.6286</v>
+      </c>
+      <c r="E50" t="n">
+        <v>412867.54</v>
+      </c>
+      <c r="F50" t="n">
+        <v>207378.36</v>
+      </c>
+      <c r="G50" t="n">
+        <v>20773.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1679,6 +1679,31 @@
         <v>20773.96</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4.9897</v>
+      </c>
+      <c r="C51" t="n">
+        <v>5.5859</v>
+      </c>
+      <c r="D51" t="n">
+        <v>6.5998</v>
+      </c>
+      <c r="E51" t="n">
+        <v>413747.72</v>
+      </c>
+      <c r="F51" t="n">
+        <v>209184.94</v>
+      </c>
+      <c r="G51" t="n">
+        <v>21023.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1704,6 +1704,31 @@
         <v>21023.6</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4.9772</v>
+      </c>
+      <c r="C52" t="n">
+        <v>5.5828</v>
+      </c>
+      <c r="D52" t="n">
+        <v>6.5983</v>
+      </c>
+      <c r="E52" t="n">
+        <v>411666.05</v>
+      </c>
+      <c r="F52" t="n">
+        <v>209066.9</v>
+      </c>
+      <c r="G52" t="n">
+        <v>20985.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1729,6 +1729,31 @@
         <v>20985.37</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4.9918</v>
+      </c>
+      <c r="C53" t="n">
+        <v>5.5828</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6.5983</v>
+      </c>
+      <c r="E53" t="n">
+        <v>414325.09</v>
+      </c>
+      <c r="F53" t="n">
+        <v>209066.9</v>
+      </c>
+      <c r="G53" t="n">
+        <v>21046.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1754,6 +1754,31 @@
         <v>21046.93</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4.9863</v>
+      </c>
+      <c r="C54" t="n">
+        <v>5.5642</v>
+      </c>
+      <c r="D54" t="n">
+        <v>6.5851</v>
+      </c>
+      <c r="E54" t="n">
+        <v>411271.27</v>
+      </c>
+      <c r="F54" t="n">
+        <v>209066.9</v>
+      </c>
+      <c r="G54" t="n">
+        <v>20886.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1779,6 +1779,31 @@
         <v>20886.11</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4.9993</v>
+      </c>
+      <c r="C55" t="n">
+        <v>5.5959</v>
+      </c>
+      <c r="D55" t="n">
+        <v>6.6228</v>
+      </c>
+      <c r="E55" t="n">
+        <v>417910.53</v>
+      </c>
+      <c r="F55" t="n">
+        <v>207463.81</v>
+      </c>
+      <c r="G55" t="n">
+        <v>20939.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1804,6 +1804,31 @@
         <v>20939.57</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>5.0465</v>
+      </c>
+      <c r="C56" t="n">
+        <v>5.609</v>
+      </c>
+      <c r="D56" t="n">
+        <v>6.654</v>
+      </c>
+      <c r="E56" t="n">
+        <v>417143.64</v>
+      </c>
+      <c r="F56" t="n">
+        <v>206887.52</v>
+      </c>
+      <c r="G56" t="n">
+        <v>20750.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1829,6 +1829,31 @@
         <v>20750.7</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>5.0524</v>
+      </c>
+      <c r="C57" t="n">
+        <v>5.6634</v>
+      </c>
+      <c r="D57" t="n">
+        <v>6.6956</v>
+      </c>
+      <c r="E57" t="n">
+        <v>406799.64</v>
+      </c>
+      <c r="F57" t="n">
+        <v>206505.98</v>
+      </c>
+      <c r="G57" t="n">
+        <v>21036.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1854,6 +1854,31 @@
         <v>21036.68</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>5.0779</v>
+      </c>
+      <c r="C58" t="n">
+        <v>5.7049</v>
+      </c>
+      <c r="D58" t="n">
+        <v>6.7663</v>
+      </c>
+      <c r="E58" t="n">
+        <v>416036.66</v>
+      </c>
+      <c r="F58" t="n">
+        <v>204324.27</v>
+      </c>
+      <c r="G58" t="n">
+        <v>21318.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1879,6 +1879,31 @@
         <v>21318.55</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>5.0693</v>
+      </c>
+      <c r="C59" t="n">
+        <v>5.7053</v>
+      </c>
+      <c r="D59" t="n">
+        <v>6.7659</v>
+      </c>
+      <c r="E59" t="n">
+        <v>413008.04</v>
+      </c>
+      <c r="F59" t="n">
+        <v>205430.33</v>
+      </c>
+      <c r="G59" t="n">
+        <v>21195.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1904,6 +1904,31 @@
         <v>21195.25</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>5.0693</v>
+      </c>
+      <c r="C60" t="n">
+        <v>5.7053</v>
+      </c>
+      <c r="D60" t="n">
+        <v>6.7659</v>
+      </c>
+      <c r="E60" t="n">
+        <v>415303.16</v>
+      </c>
+      <c r="F60" t="n">
+        <v>205430.33</v>
+      </c>
+      <c r="G60" t="n">
+        <v>21195.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1929,6 +1929,31 @@
         <v>21195.25</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>5.0596</v>
+      </c>
+      <c r="C61" t="n">
+        <v>5.673</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6.7358</v>
+      </c>
+      <c r="E61" t="n">
+        <v>415685.76</v>
+      </c>
+      <c r="F61" t="n">
+        <v>204924.56</v>
+      </c>
+      <c r="G61" t="n">
+        <v>21071.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1954,6 +1954,31 @@
         <v>21071.72</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5.0192</v>
+      </c>
+      <c r="C62" t="n">
+        <v>5.6327</v>
+      </c>
+      <c r="D62" t="n">
+        <v>6.7124</v>
+      </c>
+      <c r="E62" t="n">
+        <v>408151.56</v>
+      </c>
+      <c r="F62" t="n">
+        <v>205079.25</v>
+      </c>
+      <c r="G62" t="n">
+        <v>20766.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1979,6 +1979,31 @@
         <v>20766.44</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>5.0194</v>
+      </c>
+      <c r="C63" t="n">
+        <v>5.6366</v>
+      </c>
+      <c r="D63" t="n">
+        <v>6.724</v>
+      </c>
+      <c r="E63" t="n">
+        <v>420084.18</v>
+      </c>
+      <c r="F63" t="n">
+        <v>208821.9</v>
+      </c>
+      <c r="G63" t="n">
+        <v>20854.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2004,31 @@
         <v>20854.6</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>5.0255</v>
+      </c>
+      <c r="C64" t="n">
+        <v>5.6311</v>
+      </c>
+      <c r="D64" t="n">
+        <v>6.7237</v>
+      </c>
+      <c r="E64" t="n">
+        <v>410589.68</v>
+      </c>
+      <c r="F64" t="n">
+        <v>205515.5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>20594</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2029,6 +2029,31 @@
         <v>20594</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="C65" t="n">
+        <v>5.6476</v>
+      </c>
+      <c r="D65" t="n">
+        <v>6.7464</v>
+      </c>
+      <c r="E65" t="n">
+        <v>411615.39</v>
+      </c>
+      <c r="F65" t="n">
+        <v>204120.12</v>
+      </c>
+      <c r="G65" t="n">
+        <v>20384.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2054,31 @@
         <v>20384.28</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4.9964</v>
+      </c>
+      <c r="C66" t="n">
+        <v>5.5615</v>
+      </c>
+      <c r="D66" t="n">
+        <v>6.6395</v>
+      </c>
+      <c r="E66" t="n">
+        <v>402862.08</v>
+      </c>
+      <c r="F66" t="n">
+        <v>205082.56</v>
+      </c>
+      <c r="G66" t="n">
+        <v>20025.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2079,6 +2079,31 @@
         <v>20025.07</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>4.9964</v>
+      </c>
+      <c r="C67" t="n">
+        <v>5.5626</v>
+      </c>
+      <c r="D67" t="n">
+        <v>6.6409</v>
+      </c>
+      <c r="E67" t="n">
+        <v>401437.76</v>
+      </c>
+      <c r="F67" t="n">
+        <v>205082.56</v>
+      </c>
+      <c r="G67" t="n">
+        <v>20025.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2104,6 +2104,31 @@
         <v>20025.07</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>5.4633</v>
+      </c>
+      <c r="C68" t="n">
+        <v>5.6008</v>
+      </c>
+      <c r="D68" t="n">
+        <v>6.6805</v>
+      </c>
+      <c r="E68" t="n">
+        <v>436279.69</v>
+      </c>
+      <c r="F68" t="n">
+        <v>169681.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>21990.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2129,6 +2129,31 @@
         <v>21990.88</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>5.3113</v>
+      </c>
+      <c r="C69" t="n">
+        <v>5.9222</v>
+      </c>
+      <c r="D69" t="n">
+        <v>7.0766</v>
+      </c>
+      <c r="E69" t="n">
+        <v>425270</v>
+      </c>
+      <c r="F69" t="n">
+        <v>177456.05</v>
+      </c>
+      <c r="G69" t="n">
+        <v>21487.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2154,6 +2154,31 @@
         <v>21487.93</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>5.3712</v>
+      </c>
+      <c r="C70" t="n">
+        <v>5.9731</v>
+      </c>
+      <c r="D70" t="n">
+        <v>7.1334</v>
+      </c>
+      <c r="E70" t="n">
+        <v>432179.86</v>
+      </c>
+      <c r="F70" t="n">
+        <v>171016.48</v>
+      </c>
+      <c r="G70" t="n">
+        <v>21784.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2179,6 +2179,31 @@
         <v>21784.51</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>5.3867</v>
+      </c>
+      <c r="C71" t="n">
+        <v>6.0012</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7.1841</v>
+      </c>
+      <c r="E71" t="n">
+        <v>436268.19</v>
+      </c>
+      <c r="F71" t="n">
+        <v>170062.44</v>
+      </c>
+      <c r="G71" t="n">
+        <v>21778.43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2204,6 +2204,31 @@
         <v>21778.43</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="C72" t="n">
+        <v>6.0443</v>
+      </c>
+      <c r="D72" t="n">
+        <v>7.2556</v>
+      </c>
+      <c r="E72" t="n">
+        <v>416131.63</v>
+      </c>
+      <c r="F72" t="n">
+        <v>167791.23</v>
+      </c>
+      <c r="G72" t="n">
+        <v>21159.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cotacoes_historico.xlsx
+++ b/cotacoes_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2229,6 +2229,31 @@
         <v>21159.59</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>5.4397</v>
+      </c>
+      <c r="C73" t="n">
+        <v>6.0668</v>
+      </c>
+      <c r="D73" t="n">
+        <v>7.2814</v>
+      </c>
+      <c r="E73" t="n">
+        <v>420965.65</v>
+      </c>
+      <c r="F73" t="n">
+        <v>167921.8</v>
+      </c>
+      <c r="G73" t="n">
+        <v>21208.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
